--- a/BillyJoelMediaReferences.xlsx
+++ b/BillyJoelMediaReferences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\webroot\billyjoel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627E5423-5678-453E-8931-FC4155EB4DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5D59B8-4915-47DB-93DE-C4601B766157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{8F402856-AFFF-4594-B560-6965A850577E}"/>
+    <workbookView xWindow="2120" yWindow="580" windowWidth="29550" windowHeight="15540" xr2:uid="{8F402856-AFFF-4594-B560-6965A850577E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="416">
   <si>
     <t>Song</t>
   </si>
@@ -1278,6 +1278,15 @@
   </si>
   <si>
     <t>background song playing in a diner</t>
+  </si>
+  <si>
+    <t>The Twilight Zone</t>
+  </si>
+  <si>
+    <t>"Havana Jam"</t>
+  </si>
+  <si>
+    <t>Incorrectly quoted by the character as being in 1969 (it was 1979)</t>
   </si>
 </sst>
 </file>
@@ -1448,10 +1457,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE23F84D-052D-4A07-8A7D-9117ED843331}" name="Table1" displayName="Table1" ref="A1:G200" totalsRowShown="0">
-  <autoFilter ref="A1:G200" xr:uid="{FE23F84D-052D-4A07-8A7D-9117ED843331}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G157">
-    <sortCondition ref="C1:C157"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE23F84D-052D-4A07-8A7D-9117ED843331}" name="Table1" displayName="Table1" ref="A1:G201" totalsRowShown="0">
+  <autoFilter ref="A1:G201" xr:uid="{FE23F84D-052D-4A07-8A7D-9117ED843331}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G158">
+    <sortCondition ref="C1:C158"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1ABB8C75-D17D-4E98-9E90-C3CF8F620CB3}" name="Song"/>
@@ -1783,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B920FDF-636F-4AC2-911C-4348B1EBCDAA}">
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.08984375" bestFit="1" customWidth="1"/>
@@ -5295,55 +5304,55 @@
         <v>122</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A157" s="8" t="s">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A157" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D157" s="9">
+        <v>2019</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F157" s="10">
+        <v>3.5532407407407405E-3</v>
+      </c>
+      <c r="G157" s="11" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A158" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B157" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C157" s="8" t="s">
+      <c r="B158" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C158" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D157" s="7">
+      <c r="D158" s="7">
         <v>2019</v>
       </c>
-      <c r="E157" s="7" t="s">
+      <c r="E158" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F157" s="10">
+      <c r="F158" s="10">
         <v>2.6203703703703705E-2</v>
       </c>
-      <c r="G157" s="7" t="s">
+      <c r="G158" s="7" t="s">
         <v>297</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A158" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B158" t="s">
-        <v>50</v>
-      </c>
-      <c r="C158" t="s">
-        <v>340</v>
-      </c>
-      <c r="D158" s="7">
-        <v>2007</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F158" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>339</v>
+        <v>55</v>
       </c>
       <c r="B159" t="s">
         <v>50</v>
@@ -5352,21 +5361,21 @@
         <v>340</v>
       </c>
       <c r="D159" s="7">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F159" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
-        <v>55</v>
+        <v>339</v>
       </c>
       <c r="B160" t="s">
         <v>50</v>
@@ -5375,21 +5384,21 @@
         <v>340</v>
       </c>
       <c r="D160" s="7">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F160" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="B161" t="s">
         <v>50</v>
@@ -5397,22 +5406,22 @@
       <c r="C161" t="s">
         <v>340</v>
       </c>
-      <c r="D161" s="20">
+      <c r="D161" s="7">
         <v>2010</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F161" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="B162" t="s">
         <v>50</v>
@@ -5420,22 +5429,22 @@
       <c r="C162" t="s">
         <v>340</v>
       </c>
-      <c r="D162" s="7">
-        <v>2012</v>
+      <c r="D162" s="20">
+        <v>2010</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F162" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="B163" t="s">
         <v>50</v>
@@ -5447,18 +5456,18 @@
         <v>2012</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F163" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="B164" t="s">
         <v>50</v>
@@ -5467,21 +5476,21 @@
         <v>340</v>
       </c>
       <c r="D164" s="7">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>145</v>
+        <v>382</v>
       </c>
       <c r="F164" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="B165" t="s">
         <v>50</v>
@@ -5490,21 +5499,21 @@
         <v>340</v>
       </c>
       <c r="D165" s="7">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>385</v>
+        <v>145</v>
       </c>
       <c r="F165" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="B166" t="s">
         <v>50</v>
@@ -5513,21 +5522,21 @@
         <v>340</v>
       </c>
       <c r="D166" s="7">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F166" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="B167" t="s">
         <v>50</v>
@@ -5536,21 +5545,21 @@
         <v>340</v>
       </c>
       <c r="D167" s="7">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F167" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="B168" t="s">
         <v>50</v>
@@ -5559,21 +5568,21 @@
         <v>340</v>
       </c>
       <c r="D168" s="7">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F168" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="B169" t="s">
         <v>50</v>
@@ -5582,44 +5591,44 @@
         <v>340</v>
       </c>
       <c r="D169" s="7">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F169" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="B170" t="s">
         <v>50</v>
       </c>
       <c r="C170" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="D170" s="7">
-        <v>2003</v>
+        <v>2026</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F170" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B171" t="s">
         <v>50</v>
@@ -5637,12 +5646,12 @@
         <v>190</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="B172" t="s">
         <v>50</v>
@@ -5660,12 +5669,12 @@
         <v>190</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>294</v>
+        <v>108</v>
       </c>
       <c r="B173" t="s">
         <v>50</v>
@@ -5683,12 +5692,12 @@
         <v>190</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
-        <v>55</v>
+        <v>294</v>
       </c>
       <c r="B174" t="s">
         <v>50</v>
@@ -5706,12 +5715,12 @@
         <v>190</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
-        <v>295</v>
+        <v>55</v>
       </c>
       <c r="B175" t="s">
         <v>50</v>
@@ -5729,12 +5738,12 @@
         <v>190</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>23</v>
+        <v>295</v>
       </c>
       <c r="B176" t="s">
         <v>50</v>
@@ -5752,12 +5761,12 @@
         <v>190</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="B177" t="s">
         <v>50</v>
@@ -5766,21 +5775,21 @@
         <v>291</v>
       </c>
       <c r="D177" s="7">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>324</v>
+        <v>395</v>
       </c>
       <c r="F177" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>294</v>
+        <v>149</v>
       </c>
       <c r="B178" t="s">
         <v>50</v>
@@ -5789,21 +5798,21 @@
         <v>291</v>
       </c>
       <c r="D178" s="7">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="F178" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="B179" t="s">
         <v>50</v>
@@ -5812,21 +5821,21 @@
         <v>291</v>
       </c>
       <c r="D179" s="7">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F179" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>54</v>
+        <v>350</v>
       </c>
       <c r="B180" t="s">
         <v>50</v>
@@ -5838,18 +5847,18 @@
         <v>2009</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F180" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B181" t="s">
         <v>50</v>
@@ -5858,21 +5867,21 @@
         <v>291</v>
       </c>
       <c r="D181" s="7">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F181" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="B182" t="s">
         <v>50</v>
@@ -5890,12 +5899,12 @@
         <v>190</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="B183" t="s">
         <v>50</v>
@@ -5913,12 +5922,12 @@
         <v>190</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
-        <v>292</v>
+        <v>141</v>
       </c>
       <c r="B184" t="s">
         <v>50</v>
@@ -5936,12 +5945,12 @@
         <v>190</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="B185" t="s">
         <v>50</v>
@@ -5959,12 +5968,12 @@
         <v>190</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
-        <v>262</v>
+        <v>43</v>
       </c>
       <c r="B186" t="s">
         <v>50</v>
@@ -5982,12 +5991,12 @@
         <v>190</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
-        <v>57</v>
+        <v>262</v>
       </c>
       <c r="B187" t="s">
         <v>50</v>
@@ -6005,12 +6014,12 @@
         <v>190</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B188" t="s">
         <v>50</v>
@@ -6028,12 +6037,12 @@
         <v>190</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
-        <v>293</v>
+        <v>13</v>
       </c>
       <c r="B189" t="s">
         <v>50</v>
@@ -6051,12 +6060,12 @@
         <v>190</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
-        <v>55</v>
+        <v>293</v>
       </c>
       <c r="B190" t="s">
         <v>50</v>
@@ -6074,12 +6083,12 @@
         <v>190</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
-        <v>262</v>
+        <v>55</v>
       </c>
       <c r="B191" t="s">
         <v>50</v>
@@ -6091,18 +6100,18 @@
         <v>2012</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F191" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
-        <v>108</v>
+        <v>262</v>
       </c>
       <c r="B192" t="s">
         <v>50</v>
@@ -6111,21 +6120,21 @@
         <v>291</v>
       </c>
       <c r="D192" s="7">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F192" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="B193" t="s">
         <v>50</v>
@@ -6137,18 +6146,18 @@
         <v>2013</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F193" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="B194" t="s">
         <v>50</v>
@@ -6166,12 +6175,12 @@
         <v>190</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
-        <v>350</v>
+        <v>97</v>
       </c>
       <c r="B195" t="s">
         <v>50</v>
@@ -6180,21 +6189,21 @@
         <v>291</v>
       </c>
       <c r="D195" s="7">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F195" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
-        <v>53</v>
+        <v>350</v>
       </c>
       <c r="B196" t="s">
         <v>50</v>
@@ -6203,21 +6212,21 @@
         <v>291</v>
       </c>
       <c r="D196" s="7">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F196" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
-        <v>350</v>
+        <v>53</v>
       </c>
       <c r="B197" t="s">
         <v>50</v>
@@ -6226,16 +6235,16 @@
         <v>291</v>
       </c>
       <c r="D197" s="7">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F197" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
@@ -6252,18 +6261,18 @@
         <v>2019</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F198" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
-        <v>108</v>
+        <v>350</v>
       </c>
       <c r="B199" t="s">
         <v>50</v>
@@ -6272,21 +6281,21 @@
         <v>291</v>
       </c>
       <c r="D199" s="7">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F199" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
-        <v>350</v>
+        <v>108</v>
       </c>
       <c r="B200" t="s">
         <v>50</v>
@@ -6295,15 +6304,38 @@
         <v>291</v>
       </c>
       <c r="D200" s="7">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F200" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G200" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B201" t="s">
+        <v>50</v>
+      </c>
+      <c r="C201" t="s">
+        <v>291</v>
+      </c>
+      <c r="D201" s="7">
+        <v>2022</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F201" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G201" s="2" t="s">
         <v>371</v>
       </c>
     </row>
